--- a/artfynd/A 36365-2022 artfynd.xlsx
+++ b/artfynd/A 36365-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36365-2022 artfynd.xlsx
+++ b/artfynd/A 36365-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105406869</v>
+        <v>111670477</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558216.8534954271</v>
+        <v>558155</v>
       </c>
       <c r="R2" t="n">
-        <v>7067410.696202897</v>
+        <v>7068018</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105407253</v>
+        <v>111670497</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558169.5409389536</v>
+        <v>558160</v>
       </c>
       <c r="R3" t="n">
-        <v>7067425.776372256</v>
+        <v>7068023</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,33 +860,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105407633</v>
+        <v>111670510</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,35 +890,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558156.9451952764</v>
+        <v>558124</v>
       </c>
       <c r="R4" t="n">
-        <v>7067699.83245489</v>
+        <v>7067994</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,33 +962,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105407020</v>
+        <v>111670558</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,35 +992,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558214.3430314056</v>
+        <v>558134</v>
       </c>
       <c r="R5" t="n">
-        <v>7067354.371003789</v>
+        <v>7067979</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,33 +1064,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105407777</v>
+        <v>111670567</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,35 +1094,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558129.6150870904</v>
+        <v>558130</v>
       </c>
       <c r="R6" t="n">
-        <v>7067738.320907875</v>
+        <v>7067958</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,22 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,33 +1166,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105406812</v>
+        <v>111670575</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,35 +1196,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>620</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558287.4598545628</v>
+        <v>558083</v>
       </c>
       <c r="R7" t="n">
-        <v>7067359.709299644</v>
+        <v>7067975</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,22 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,33 +1268,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105407476</v>
+        <v>105407855</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558150.3961111513</v>
+        <v>558103</v>
       </c>
       <c r="R8" t="n">
-        <v>7067597.798007657</v>
+        <v>7067761</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1356,9 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105407270</v>
+        <v>111671201</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,35 +1396,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558169.5000997323</v>
+        <v>558250</v>
       </c>
       <c r="R9" t="n">
-        <v>7067427.991290601</v>
+        <v>7067937</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,22 +1453,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,33 +1467,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105407296</v>
+        <v>111671226</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,35 +1497,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyran, Ång</t>
+          <t>Lökåsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558186.7468125005</v>
+        <v>558119</v>
       </c>
       <c r="R10" t="n">
-        <v>7067479.26935647</v>
+        <v>7067742</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,22 +1554,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,55 +1568,51 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105407737</v>
+        <v>105406812</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558150.4280862501</v>
+        <v>558287</v>
       </c>
       <c r="R11" t="n">
-        <v>7067740.476877268</v>
+        <v>7067360</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1656,9 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,19 +1685,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105407616</v>
+        <v>105406869</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1846,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558156.0989656385</v>
+        <v>558217</v>
       </c>
       <c r="R12" t="n">
-        <v>7067697.60137299</v>
+        <v>7067411</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,19 +1754,9 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,37 +1783,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105407682</v>
+        <v>105407020</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558151.7724037775</v>
+        <v>558215</v>
       </c>
       <c r="R13" t="n">
-        <v>7067715.688507118</v>
+        <v>7067354</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,19 +1852,9 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-12-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,56 +1881,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105482502</v>
+        <v>105407253</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>nära Vängel, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558138.9040931723</v>
+        <v>558170</v>
       </c>
       <c r="R14" t="n">
-        <v>7067956.485104631</v>
+        <v>7067426</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,96 +1950,78 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105482412</v>
+        <v>105407270</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>nära Vängel, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558252.0995944706</v>
+        <v>558170</v>
       </c>
       <c r="R15" t="n">
-        <v>7067928.888419926</v>
+        <v>7067428</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2223,100 +2048,78 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105482201</v>
+        <v>105407296</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>nära Vängel, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558278.285834157</v>
+        <v>558187</v>
       </c>
       <c r="R16" t="n">
-        <v>7067616.109990587</v>
+        <v>7067479</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,96 +2146,78 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105482298</v>
+        <v>105407476</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>nära Vängel, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558322.9904916538</v>
+        <v>558150</v>
       </c>
       <c r="R17" t="n">
-        <v>7067717.963325187</v>
+        <v>7067598</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2459,100 +2244,78 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105481976</v>
+        <v>105407616</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>nära Vängel, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558157.6617459382</v>
+        <v>558156</v>
       </c>
       <c r="R18" t="n">
-        <v>7067564.69850278</v>
+        <v>7067698</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2579,93 +2342,75 @@
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-12-30</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111671188</v>
+        <v>105407935</v>
       </c>
       <c r="B19" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558216</v>
+        <v>558101</v>
       </c>
       <c r="R19" t="n">
-        <v>7067869</v>
+        <v>7067763</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2692,12 +2437,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,34 +2451,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111670558</v>
+        <v>105407633</v>
       </c>
       <c r="B20" t="n">
-        <v>96346</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,38 +2480,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558134</v>
+        <v>558157</v>
       </c>
       <c r="R20" t="n">
-        <v>7067979</v>
+        <v>7067700</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2799,12 +2535,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,34 +2549,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111670510</v>
+        <v>105407682</v>
       </c>
       <c r="B21" t="n">
-        <v>96346</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,38 +2578,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558124</v>
+        <v>558152</v>
       </c>
       <c r="R21" t="n">
-        <v>7067994</v>
+        <v>7067716</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2906,12 +2633,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,34 +2647,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111671179</v>
+        <v>105407737</v>
       </c>
       <c r="B22" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,19 +2694,17 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558216</v>
+        <v>558151</v>
       </c>
       <c r="R22" t="n">
-        <v>7067868</v>
+        <v>7067741</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3012,12 +2731,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,34 +2745,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111670477</v>
+        <v>105407777</v>
       </c>
       <c r="B23" t="n">
-        <v>96346</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,38 +2774,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558155</v>
+        <v>558130</v>
       </c>
       <c r="R23" t="n">
-        <v>7068017</v>
+        <v>7067738</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3119,12 +2829,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3133,34 +2843,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111671226</v>
+        <v>105481976</v>
       </c>
       <c r="B24" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,40 +2872,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>nära Vängel, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558118</v>
+        <v>558158</v>
       </c>
       <c r="R24" t="n">
-        <v>7067742</v>
+        <v>7067565</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3225,12 +2933,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,27 +2954,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111671294</v>
+        <v>105482201</v>
       </c>
       <c r="B25" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,22 +2995,26 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>nära Vängel, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558118</v>
+        <v>558278</v>
       </c>
       <c r="R25" t="n">
-        <v>7067742</v>
+        <v>7067616</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3331,12 +3038,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,49 +3059,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111671190</v>
+        <v>105482298</v>
       </c>
       <c r="B26" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,17 +3105,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>nära Vängel, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558216</v>
+        <v>558323</v>
       </c>
       <c r="R26" t="n">
-        <v>7067869</v>
+        <v>7067718</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3437,12 +3139,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,27 +3160,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111670497</v>
+        <v>105482412</v>
       </c>
       <c r="B27" t="n">
-        <v>96346</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,41 +3183,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>nära Vängel, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558160</v>
+        <v>558252</v>
       </c>
       <c r="R27" t="n">
-        <v>7068023</v>
+        <v>7067929</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,12 +3240,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3565,27 +3261,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111671197</v>
+        <v>105482502</v>
       </c>
       <c r="B28" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,17 +3307,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lökåsberget, Ång</t>
+          <t>nära Vängel, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558250</v>
+        <v>558138</v>
       </c>
       <c r="R28" t="n">
-        <v>7067937</v>
+        <v>7067956</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3650,12 +3341,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,27 +3362,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111671201</v>
+        <v>111671179</v>
       </c>
       <c r="B29" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3699,21 +3385,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3726,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558250</v>
+        <v>558216</v>
       </c>
       <c r="R29" t="n">
-        <v>7067937</v>
+        <v>7067867</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3789,15 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111670567</v>
+        <v>111671197</v>
       </c>
       <c r="B30" t="n">
-        <v>96346</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,27 +3486,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3833,10 +3513,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558130</v>
+        <v>558250</v>
       </c>
       <c r="R30" t="n">
-        <v>7067959</v>
+        <v>7067937</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3893,6 +3573,309 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111671294</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lökåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>558119</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7067742</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>111671188</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lökåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>558215</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7067870</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111671190</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lökåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>558215</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7067870</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36365-2022 artfynd.xlsx
+++ b/artfynd/A 36365-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670477</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670558</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111670575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105406812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105406869</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1878,6 +1938,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407020</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1976,6 +2041,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407253</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407270</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407296</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2270,6 +2350,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407476</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2368,6 +2453,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407616</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2466,6 +2556,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407935</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2564,6 +2659,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407633</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2662,6 +2762,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407682</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2760,6 +2865,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407737</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105407777</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105481976</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3068,6 +3188,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105482201</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3169,6 +3294,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105482298</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3270,6 +3400,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105482412</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3371,6 +3506,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105482502</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3472,6 +3612,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671179</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671197</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3674,6 +3824,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671294</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3775,6 +3930,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671188</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3876,8 +4036,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111671190</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>